--- a/Processing of experimental data/Lab 3/Lab3.xlsx
+++ b/Processing of experimental data/Lab 3/Lab3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Prog\BSUIR-Labs\Processing of experimental data\Lab 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1543D7-9462-464C-87C7-1D53ABE33974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3630A469-0951-494E-8409-5D070595A6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{68418C94-6E50-41DE-9C16-B716F6666BB9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{68418C94-6E50-41DE-9C16-B716F6666BB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
   <si>
     <t>t</t>
   </si>
@@ -49,12 +49,240 @@
   <si>
     <t>xt</t>
   </si>
+  <si>
+    <t>a1=</t>
+  </si>
+  <si>
+    <t>delta(x)=</t>
+  </si>
+  <si>
+    <t>delta(y)=</t>
+  </si>
+  <si>
+    <t>Задание 3</t>
+  </si>
+  <si>
+    <t>a0=y1-x1*a1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">тогда а0 = </t>
+  </si>
+  <si>
+    <t>Задание 4</t>
+  </si>
+  <si>
+    <t>xt^2</t>
+  </si>
+  <si>
+    <t>xt-xa</t>
+  </si>
+  <si>
+    <t>xa - x avg</t>
+  </si>
+  <si>
+    <t>(xt-xa)^2</t>
+  </si>
+  <si>
+    <t>ya - y avg</t>
+  </si>
+  <si>
+    <t>yt-ya</t>
+  </si>
+  <si>
+    <t>(yt-ya)^2</t>
+  </si>
+  <si>
+    <t>(xt-xa)(yt-ya)</t>
+  </si>
+  <si>
+    <t>Среднее</t>
+  </si>
+  <si>
+    <t>Сумма</t>
+  </si>
+  <si>
+    <t>Задание 5</t>
+  </si>
+  <si>
+    <t>a1=Sxy/Sxx</t>
+  </si>
+  <si>
+    <t>=&gt;</t>
+  </si>
+  <si>
+    <t>a0=ya-xa*a1</t>
+  </si>
+  <si>
+    <t>a0 =</t>
+  </si>
+  <si>
+    <t>a1 =</t>
+  </si>
+  <si>
+    <t>yh - y hat</t>
+  </si>
+  <si>
+    <t>yht</t>
+  </si>
+  <si>
+    <t>et</t>
+  </si>
+  <si>
+    <t>et^2</t>
+  </si>
+  <si>
+    <t>st^2</t>
+  </si>
+  <si>
+    <t>Задание 6-7</t>
+  </si>
+  <si>
+    <t>s1- несмещённая оценка дисперсии переменной a1</t>
+  </si>
+  <si>
+    <t>Задание 8-9</t>
+  </si>
+  <si>
+    <t>s0- несмещённая оценка дисперсии переменной a0</t>
+  </si>
+  <si>
+    <t>s1^2=</t>
+  </si>
+  <si>
+    <t>s0^2=</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>Да</t>
+  </si>
+  <si>
+    <t>tнабл &gt; t крит</t>
+  </si>
+  <si>
+    <t>t крит</t>
+  </si>
+  <si>
+    <t>Значим а1?</t>
+  </si>
+  <si>
+    <t>tнабл1=</t>
+  </si>
+  <si>
+    <t>tнабл0=</t>
+  </si>
+  <si>
+    <t>Значим а0?</t>
+  </si>
+  <si>
+    <t>Задание 10-14</t>
+  </si>
+  <si>
+    <t>ДИа1 Н</t>
+  </si>
+  <si>
+    <t>ДИа1 В</t>
+  </si>
+  <si>
+    <t>ДИа0 Н</t>
+  </si>
+  <si>
+    <t>ДИа0 В</t>
+  </si>
+  <si>
+    <t>Задание 15</t>
+  </si>
+  <si>
+    <t>R^2=</t>
+  </si>
+  <si>
+    <t>Это высокий показатель, указывающий на хорошее качество подгонки модели к данным.</t>
+  </si>
+  <si>
+    <r>
+      <t>Коэффициент детерминации показывает долю дисперсии зависимой переменно</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>й</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">, объяснённую моделью. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Значение R2=0,8371 означает, что модель объясняет 83,7% вариации.</t>
+  </si>
+  <si>
+    <t>Значима?</t>
+  </si>
+  <si>
+    <t>F=</t>
+  </si>
+  <si>
+    <t>Задание 16-17</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>yh</t>
+  </si>
+  <si>
+    <t>ДИН1</t>
+  </si>
+  <si>
+    <t>ДИВ1</t>
+  </si>
+  <si>
+    <t>ДИН2</t>
+  </si>
+  <si>
+    <t>ДИВ2</t>
+  </si>
+  <si>
+    <t>ДИН3</t>
+  </si>
+  <si>
+    <t>ДИВ3</t>
+  </si>
+  <si>
+    <t>Задание 18-19</t>
+  </si>
+  <si>
+    <t>Задание 20</t>
+  </si>
+  <si>
+    <t>Задание 21</t>
+  </si>
+  <si>
+    <t>Построенный график остатков свидетельствует об отсутствии явной автокорреляции и систематического тренда.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Остатки распределены случайным образом относительно нулевой линии, их дисперсия визуально стабильна (гомоскедастичность). </t>
+  </si>
+  <si>
+    <t>Это позволяет считать предпосылки метода наименьших квадратов выполненными, а модель – адекватной.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +291,74 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -84,8 +373,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -523,7 +840,1446 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>График</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$B$102:$B$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>217.97467792092402</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>225.82541092847623</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>233.67614393602844</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>241.52687694358065</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>249.37760995113283</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>257.228342958685</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>265.07907596623721</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>272.92980897378942</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>280.78054198134163</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-574A-48AF-B3CB-4112901C19E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>ДИН1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$C$102:$C$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>211.57266457010775</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>220.57587069721512</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>229.41727564940459</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>237.95943608582644</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>246.01253963806056</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>253.49616518989521</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>260.54663817500835</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>267.34722690878999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>274.0132795037124</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-574A-48AF-B3CB-4112901C19E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>ДИН2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$E$102:$E$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>210.21825485817195</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>219.46527815658709</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>228.51626962939633</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>237.2047084275527</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>245.30062548486831</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>252.70658579670709</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>259.58775580054368</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>266.16617604991455</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>272.58159769977624</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-574A-48AF-B3CB-4112901C19E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>ДИН3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$G$102:$G$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>207.34772383130573</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>217.1114923575156</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>226.60668074131138</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>235.60514136832623</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>243.79179721289529</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>251.03315409701756</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>257.55550397691934</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>263.66306114691855</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>269.54729648162817</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-574A-48AF-B3CB-4112901C19E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>ДИВ1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$D$102:$D$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>224.3766912717403</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>231.07495115973734</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>237.93501222265229</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>245.09431780133485</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>252.74268026420509</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>260.96052072747483</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>269.61151375746607</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>278.51239103878885</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>287.54780445897086</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-574A-48AF-B3CB-4112901C19E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>ДИВ2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$F$102:$F$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>225.7311009836761</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>232.18554370036537</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>238.83601824266054</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>245.84904545960859</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>253.45459441739735</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>261.75010012066292</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>270.57039613193075</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>279.69344189766429</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>288.97948626290702</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-574A-48AF-B3CB-4112901C19E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>ДИВ3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$H$102:$H$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>228.60163201054232</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>234.53932949943686</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>240.7456071307455</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>247.44861251883506</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>254.96342268937036</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>263.42353182035242</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>272.60264795555508</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>282.19655680066029</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>292.01378748105509</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-574A-48AF-B3CB-4112901C19E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="70752352"/>
+        <c:axId val="70752832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="70752352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="20"/>
+          <c:min val="12"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70752832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="70752832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="211"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70752352"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-BY"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>et</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$A$54:$A$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$K$54:$K$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>-11.676143936028438</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8.3776099511328255</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-14.228342958685005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.07019102621058</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-12.079075966237212</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4731230564193538</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.323856063971562</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.920924033762788</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.7716570413149952</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.473123056419354</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.1745890715237692</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.37760995113282547</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.2283429586850048</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.0701910262105798</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-3.0790759662372125</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-5.7805419813416279</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-6.9746779209240231</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.1745890715237692</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.5322079075976944E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-1.6761439360284385</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-15B3-412A-A731-C348677DF7FB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="71143840"/>
+        <c:axId val="71144320"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="71143840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="71144320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="71144320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="71143840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-BY"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1047,6 +2803,1038 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -1099,6 +3887,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28DC15C5-D5F7-CE28-3D74-DBE99CA79C72}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>149</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>1950720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48FF775F-3270-1FF3-257D-7A938CAB372B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1424,21 +4284,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07ADB6A5-F5E5-4D9C-8161-8FDAE37DE16A}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:O172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1448,8 +4317,11 @@
       <c r="C2">
         <v>222</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="M2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1459,8 +4331,15 @@
       <c r="C3">
         <v>241</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3">
+        <f>N5/N4</f>
+        <v>7.5625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1470,8 +4349,15 @@
       <c r="C4">
         <v>243</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="M4" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4">
+        <f>B17-B20</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1481,8 +4367,15 @@
       <c r="C5">
         <v>285</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="M5" t="s">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>C17-(C20+C18)/2</f>
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1493,7 +4386,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1503,8 +4396,18 @@
       <c r="C7">
         <v>247</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7">
+        <f>C2-B2*N3</f>
+        <v>116.125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1515,7 +4418,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1526,7 +4429,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1537,7 +4440,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1548,7 +4451,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1559,7 +4462,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1570,7 +4473,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1581,7 +4484,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1592,7 +4495,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1603,7 +4506,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1614,7 +4517,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1625,7 +4528,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1636,7 +4539,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1647,7 +4550,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1658,8 +4561,2673 @@
         <v>232</v>
       </c>
     </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25">
+        <v>14</v>
+      </c>
+      <c r="C25">
+        <v>222</v>
+      </c>
+      <c r="D25">
+        <f>B25*B25</f>
+        <v>196</v>
+      </c>
+      <c r="E25">
+        <f>B25-B46</f>
+        <v>-1.8499999999999996</v>
+      </c>
+      <c r="F25">
+        <f>E25*E25</f>
+        <v>3.4224999999999985</v>
+      </c>
+      <c r="G25">
+        <f>C25-C46</f>
+        <v>-26.199999999999989</v>
+      </c>
+      <c r="H25">
+        <f>G25*G25</f>
+        <v>686.43999999999937</v>
+      </c>
+      <c r="I25">
+        <f>E25*G25</f>
+        <v>48.46999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>16</v>
+      </c>
+      <c r="C26">
+        <v>241</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ref="D26:D44" si="0">B26*B26</f>
+        <v>256</v>
+      </c>
+      <c r="E26">
+        <f>B26-B46</f>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="F26">
+        <f t="shared" ref="F26:F44" si="1">E26*E26</f>
+        <v>2.2500000000000107E-2</v>
+      </c>
+      <c r="G26">
+        <f>C26-C46</f>
+        <v>-7.1999999999999886</v>
+      </c>
+      <c r="H26">
+        <f t="shared" ref="H26:H44" si="2">G26*G26</f>
+        <v>51.839999999999833</v>
+      </c>
+      <c r="I26">
+        <f t="shared" ref="I26:I44" si="3">E26*G26</f>
+        <v>-1.080000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>17</v>
+      </c>
+      <c r="C27">
+        <v>243</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>289</v>
+      </c>
+      <c r="E27">
+        <f>B27-B46</f>
+        <v>1.1500000000000004</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>1.3225000000000009</v>
+      </c>
+      <c r="G27">
+        <f>C27-C46</f>
+        <v>-5.1999999999999886</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="2"/>
+        <v>27.039999999999882</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>-5.9799999999999889</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>19</v>
+      </c>
+      <c r="C28">
+        <v>285</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>361</v>
+      </c>
+      <c r="E28">
+        <f>B28-B46</f>
+        <v>3.1500000000000004</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>9.922500000000003</v>
+      </c>
+      <c r="G28">
+        <f>C28-C46</f>
+        <v>36.800000000000011</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="2"/>
+        <v>1354.2400000000009</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="3"/>
+        <v>115.92000000000004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>18</v>
+      </c>
+      <c r="C29">
+        <v>253</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>324</v>
+      </c>
+      <c r="E29">
+        <f>B29-B46</f>
+        <v>2.1500000000000004</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>4.6225000000000014</v>
+      </c>
+      <c r="G29">
+        <f>C29-C46</f>
+        <v>4.8000000000000114</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="2"/>
+        <v>23.040000000000109</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="3"/>
+        <v>10.320000000000027</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
+      <c r="C30">
+        <v>247</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>225</v>
+      </c>
+      <c r="E30">
+        <f>B30-B46</f>
+        <v>-0.84999999999999964</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>0.72249999999999936</v>
+      </c>
+      <c r="G30">
+        <f>C30-C46</f>
+        <v>-1.1999999999999886</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="2"/>
+        <v>1.4399999999999726</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="3"/>
+        <v>1.0199999999999898</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>14</v>
+      </c>
+      <c r="C31">
+        <v>246</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>196</v>
+      </c>
+      <c r="E31">
+        <f>B31-B46</f>
+        <v>-1.8499999999999996</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>3.4224999999999985</v>
+      </c>
+      <c r="G31">
+        <f>C31-C46</f>
+        <v>-2.1999999999999886</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="2"/>
+        <v>4.8399999999999501</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="3"/>
+        <v>4.0699999999999781</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>8</v>
+      </c>
+      <c r="B32">
+        <v>18</v>
+      </c>
+      <c r="C32">
+        <v>276</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>324</v>
+      </c>
+      <c r="E32">
+        <f>B32-B46</f>
+        <v>2.1500000000000004</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>4.6225000000000014</v>
+      </c>
+      <c r="G32">
+        <f>C32-C46</f>
+        <v>27.800000000000011</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="2"/>
+        <v>772.8400000000006</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="3"/>
+        <v>59.770000000000032</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>17</v>
+      </c>
+      <c r="C33">
+        <v>261</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>289</v>
+      </c>
+      <c r="E33">
+        <f>B33-B46</f>
+        <v>1.1500000000000004</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="1"/>
+        <v>1.3225000000000009</v>
+      </c>
+      <c r="G33">
+        <f>C33-C46</f>
+        <v>12.800000000000011</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="2"/>
+        <v>163.84000000000029</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="3"/>
+        <v>14.720000000000018</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>254</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>225</v>
+      </c>
+      <c r="E34">
+        <f>B34-B46</f>
+        <v>-0.84999999999999964</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>0.72249999999999936</v>
+      </c>
+      <c r="G34">
+        <f>C34-C46</f>
+        <v>5.8000000000000114</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="2"/>
+        <v>33.640000000000128</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="3"/>
+        <v>-4.9300000000000077</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="B35">
+        <v>13</v>
+      </c>
+      <c r="C35">
+        <v>229</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>169</v>
+      </c>
+      <c r="E35">
+        <f>B35-B46</f>
+        <v>-2.8499999999999996</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>8.1224999999999987</v>
+      </c>
+      <c r="G35">
+        <f>C35-C46</f>
+        <v>-19.199999999999989</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="2"/>
+        <v>368.63999999999959</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="3"/>
+        <v>54.719999999999963</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>12</v>
+      </c>
+      <c r="B36">
+        <v>16</v>
+      </c>
+      <c r="C36">
+        <v>249</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>256</v>
+      </c>
+      <c r="E36">
+        <f>B36-B46</f>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>2.2500000000000107E-2</v>
+      </c>
+      <c r="G36">
+        <f>C36-C46</f>
+        <v>0.80000000000001137</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="2"/>
+        <v>0.64000000000001822</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="3"/>
+        <v>0.12000000000000199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>13</v>
+      </c>
+      <c r="B37">
+        <v>17</v>
+      </c>
+      <c r="C37">
+        <v>252</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>289</v>
+      </c>
+      <c r="E37">
+        <f>B37-B46</f>
+        <v>1.1500000000000004</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="1"/>
+        <v>1.3225000000000009</v>
+      </c>
+      <c r="G37">
+        <f>C37-C46</f>
+        <v>3.8000000000000114</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="2"/>
+        <v>14.440000000000087</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="3"/>
+        <v>4.3700000000000143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>279</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="0"/>
+        <v>361</v>
+      </c>
+      <c r="E38">
+        <f>B38-B46</f>
+        <v>3.1500000000000004</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>9.922500000000003</v>
+      </c>
+      <c r="G38">
+        <f>C38-C46</f>
+        <v>30.800000000000011</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="2"/>
+        <v>948.64000000000067</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="3"/>
+        <v>97.020000000000053</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39">
+        <v>18</v>
+      </c>
+      <c r="C39">
+        <v>262</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>324</v>
+      </c>
+      <c r="E39">
+        <f>B39-B46</f>
+        <v>2.1500000000000004</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>4.6225000000000014</v>
+      </c>
+      <c r="G39">
+        <f>C39-C46</f>
+        <v>13.800000000000011</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="2"/>
+        <v>190.44000000000031</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="3"/>
+        <v>29.67000000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>16</v>
+      </c>
+      <c r="B40">
+        <v>20</v>
+      </c>
+      <c r="C40">
+        <v>275</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="E40">
+        <f>B40-B46</f>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>17.222500000000004</v>
+      </c>
+      <c r="G40">
+        <f>C40-C46</f>
+        <v>26.800000000000011</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="2"/>
+        <v>718.24000000000058</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="3"/>
+        <v>111.22000000000006</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>17</v>
+      </c>
+      <c r="B41">
+        <v>12</v>
+      </c>
+      <c r="C41">
+        <v>211</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>144</v>
+      </c>
+      <c r="E41">
+        <f>B41-B46</f>
+        <v>-3.8499999999999996</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>14.822499999999998</v>
+      </c>
+      <c r="G41">
+        <f>C41-C46</f>
+        <v>-37.199999999999989</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="2"/>
+        <v>1383.8399999999992</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="3"/>
+        <v>143.21999999999994</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>18</v>
+      </c>
+      <c r="B42">
+        <v>13</v>
+      </c>
+      <c r="C42">
+        <v>229</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>169</v>
+      </c>
+      <c r="E42">
+        <f>B42-B46</f>
+        <v>-2.8499999999999996</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>8.1224999999999987</v>
+      </c>
+      <c r="G42">
+        <f>C42-C46</f>
+        <v>-19.199999999999989</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="2"/>
+        <v>368.63999999999959</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="3"/>
+        <v>54.719999999999963</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>19</v>
+      </c>
+      <c r="B43">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>218</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>144</v>
+      </c>
+      <c r="E43">
+        <f>B43-B46</f>
+        <v>-3.8499999999999996</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>14.822499999999998</v>
+      </c>
+      <c r="G43">
+        <f>C43-C46</f>
+        <v>-30.199999999999989</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="2"/>
+        <v>912.03999999999928</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="3"/>
+        <v>116.26999999999994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>20</v>
+      </c>
+      <c r="B44">
+        <v>14</v>
+      </c>
+      <c r="C44">
+        <v>232</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="0"/>
+        <v>196</v>
+      </c>
+      <c r="E44">
+        <f>B44-B46</f>
+        <v>-1.8499999999999996</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>3.4224999999999985</v>
+      </c>
+      <c r="G44">
+        <f>C44-C46</f>
+        <v>-16.199999999999989</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="2"/>
+        <v>262.43999999999966</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="3"/>
+        <v>29.969999999999974</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" s="3">
+        <f>SUM(B25:B44)</f>
+        <v>317</v>
+      </c>
+      <c r="C45" s="3">
+        <f>SUM(C25:C44)</f>
+        <v>4964</v>
+      </c>
+      <c r="D45" s="3">
+        <f>SUM(D25:D44)</f>
+        <v>5137</v>
+      </c>
+      <c r="E45" s="3">
+        <f>SUM(E25:E44)</f>
+        <v>7.1054273576010019E-15</v>
+      </c>
+      <c r="F45" s="3">
+        <f t="shared" ref="F45:I45" si="4">SUM(F25:F44)</f>
+        <v>112.55</v>
+      </c>
+      <c r="G45" s="3">
+        <f t="shared" si="4"/>
+        <v>2.2737367544323206E-13</v>
+      </c>
+      <c r="H45" s="3">
+        <f t="shared" si="4"/>
+        <v>8287.2000000000007</v>
+      </c>
+      <c r="I45" s="3">
+        <f t="shared" si="4"/>
+        <v>883.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="3">
+        <f>AVERAGE(B25:B44)</f>
+        <v>15.85</v>
+      </c>
+      <c r="C46" s="3">
+        <f>AVERAGE(C25:C44)</f>
+        <v>248.2</v>
+      </c>
+      <c r="D46" s="3">
+        <f>AVERAGE(D25:D44)</f>
+        <v>256.85000000000002</v>
+      </c>
+      <c r="E46" s="3">
+        <f>AVERAGE(E25:E44)</f>
+        <v>3.5527136788005011E-16</v>
+      </c>
+      <c r="F46" s="3">
+        <f t="shared" ref="F46:I46" si="5">AVERAGE(F25:F44)</f>
+        <v>5.6274999999999995</v>
+      </c>
+      <c r="G46" s="3">
+        <f t="shared" si="5"/>
+        <v>1.1368683772161604E-14</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="5"/>
+        <v>414.36</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="5"/>
+        <v>44.18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="8">
+        <f>I45/F45</f>
+        <v>7.8507330075521997</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50">
+        <f>C46-B46*D49</f>
+        <v>123.76588183029763</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1</v>
+      </c>
+      <c r="B54">
+        <v>14</v>
+      </c>
+      <c r="C54">
+        <v>222</v>
+      </c>
+      <c r="D54">
+        <f>B54*B54</f>
+        <v>196</v>
+      </c>
+      <c r="E54">
+        <f>B54-B75</f>
+        <v>-1.8499999999999996</v>
+      </c>
+      <c r="F54">
+        <f>E54*E54</f>
+        <v>3.4224999999999985</v>
+      </c>
+      <c r="G54">
+        <f>C54-C75</f>
+        <v>-26.199999999999989</v>
+      </c>
+      <c r="H54">
+        <f>G54*G54</f>
+        <v>686.43999999999937</v>
+      </c>
+      <c r="I54">
+        <f>E54*G54</f>
+        <v>48.46999999999997</v>
+      </c>
+      <c r="J54">
+        <f>$D$50+$D$49*B54</f>
+        <v>233.67614393602844</v>
+      </c>
+      <c r="K54">
+        <f>C54-J54</f>
+        <v>-11.676143936028438</v>
+      </c>
+      <c r="L54">
+        <f>K54^2</f>
+        <v>136.33233721485368</v>
+      </c>
+      <c r="M54">
+        <f>L54/18</f>
+        <v>7.5740187341585381</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>2</v>
+      </c>
+      <c r="B55">
+        <v>16</v>
+      </c>
+      <c r="C55">
+        <v>241</v>
+      </c>
+      <c r="D55">
+        <f t="shared" ref="D55:D73" si="6">B55*B55</f>
+        <v>256</v>
+      </c>
+      <c r="E55">
+        <f>B55-B75</f>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="F55">
+        <f t="shared" ref="F55:F73" si="7">E55*E55</f>
+        <v>2.2500000000000107E-2</v>
+      </c>
+      <c r="G55">
+        <f>C55-C75</f>
+        <v>-7.1999999999999886</v>
+      </c>
+      <c r="H55">
+        <f t="shared" ref="H55:H73" si="8">G55*G55</f>
+        <v>51.839999999999833</v>
+      </c>
+      <c r="I55">
+        <f t="shared" ref="I55:I73" si="9">E55*G55</f>
+        <v>-1.080000000000001</v>
+      </c>
+      <c r="J55">
+        <f t="shared" ref="J55:J73" si="10">$D$50+$D$49*B55</f>
+        <v>249.37760995113283</v>
+      </c>
+      <c r="K55">
+        <f t="shared" ref="K55:K73" si="11">C55-J55</f>
+        <v>-8.3776099511328255</v>
+      </c>
+      <c r="L55">
+        <f t="shared" ref="L55:L73" si="12">K55^2</f>
+        <v>70.184348493319746</v>
+      </c>
+      <c r="M55">
+        <f t="shared" ref="M55:M73" si="13">L55/18</f>
+        <v>3.8991304718510968</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56">
+        <v>17</v>
+      </c>
+      <c r="C56">
+        <v>243</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="6"/>
+        <v>289</v>
+      </c>
+      <c r="E56">
+        <f>B56-B75</f>
+        <v>1.1500000000000004</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="7"/>
+        <v>1.3225000000000009</v>
+      </c>
+      <c r="G56">
+        <f>C56-C75</f>
+        <v>-5.1999999999999886</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="8"/>
+        <v>27.039999999999882</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="9"/>
+        <v>-5.9799999999999889</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="10"/>
+        <v>257.228342958685</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="11"/>
+        <v>-14.228342958685005</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="12"/>
+        <v>202.44574334996116</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="13"/>
+        <v>11.24698574166451</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>4</v>
+      </c>
+      <c r="B57">
+        <v>19</v>
+      </c>
+      <c r="C57">
+        <v>285</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="6"/>
+        <v>361</v>
+      </c>
+      <c r="E57">
+        <f>B57-B75</f>
+        <v>3.1500000000000004</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="7"/>
+        <v>9.922500000000003</v>
+      </c>
+      <c r="G57">
+        <f>C57-C75</f>
+        <v>36.800000000000011</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="8"/>
+        <v>1354.2400000000009</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="9"/>
+        <v>115.92000000000004</v>
+      </c>
+      <c r="J57">
+        <f t="shared" si="10"/>
+        <v>272.92980897378942</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="11"/>
+        <v>12.07019102621058</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="12"/>
+        <v>145.68951140921442</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="13"/>
+        <v>8.0938617449563566</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>5</v>
+      </c>
+      <c r="B58">
+        <v>18</v>
+      </c>
+      <c r="C58">
+        <v>253</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="6"/>
+        <v>324</v>
+      </c>
+      <c r="E58">
+        <f>B58-B75</f>
+        <v>2.1500000000000004</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="7"/>
+        <v>4.6225000000000014</v>
+      </c>
+      <c r="G58">
+        <f>C58-C75</f>
+        <v>4.8000000000000114</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="8"/>
+        <v>23.040000000000109</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="9"/>
+        <v>10.320000000000027</v>
+      </c>
+      <c r="J58">
+        <f t="shared" si="10"/>
+        <v>265.07907596623721</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="11"/>
+        <v>-12.079075966237212</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="12"/>
+        <v>145.90407619812945</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="13"/>
+        <v>8.1057820110071912</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>6</v>
+      </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
+      <c r="C59">
+        <v>247</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="6"/>
+        <v>225</v>
+      </c>
+      <c r="E59">
+        <f>B59-B75</f>
+        <v>-0.84999999999999964</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="7"/>
+        <v>0.72249999999999936</v>
+      </c>
+      <c r="G59">
+        <f>C59-C75</f>
+        <v>-1.1999999999999886</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="8"/>
+        <v>1.4399999999999726</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="9"/>
+        <v>1.0199999999999898</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="10"/>
+        <v>241.52687694358065</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="11"/>
+        <v>5.4731230564193538</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="12"/>
+        <v>29.95507599070913</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="13"/>
+        <v>1.6641708883727295</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>7</v>
+      </c>
+      <c r="B60">
+        <v>14</v>
+      </c>
+      <c r="C60">
+        <v>246</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="6"/>
+        <v>196</v>
+      </c>
+      <c r="E60">
+        <f>B60-B75</f>
+        <v>-1.8499999999999996</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="7"/>
+        <v>3.4224999999999985</v>
+      </c>
+      <c r="G60">
+        <f>C60-C75</f>
+        <v>-2.1999999999999886</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="8"/>
+        <v>4.8399999999999501</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="9"/>
+        <v>4.0699999999999781</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="10"/>
+        <v>233.67614393602844</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="11"/>
+        <v>12.323856063971562</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="12"/>
+        <v>151.87742828548863</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="13"/>
+        <v>8.4376349047493679</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>8</v>
+      </c>
+      <c r="B61">
+        <v>18</v>
+      </c>
+      <c r="C61">
+        <v>276</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="6"/>
+        <v>324</v>
+      </c>
+      <c r="E61">
+        <f>B61-B75</f>
+        <v>2.1500000000000004</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="7"/>
+        <v>4.6225000000000014</v>
+      </c>
+      <c r="G61">
+        <f>C61-C75</f>
+        <v>27.800000000000011</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="8"/>
+        <v>772.8400000000006</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="9"/>
+        <v>59.770000000000032</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="10"/>
+        <v>265.07907596623721</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="11"/>
+        <v>10.920924033762788</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="12"/>
+        <v>119.26658175121767</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="13"/>
+        <v>6.6259212084009818</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>9</v>
+      </c>
+      <c r="B62">
+        <v>17</v>
+      </c>
+      <c r="C62">
+        <v>261</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="6"/>
+        <v>289</v>
+      </c>
+      <c r="E62">
+        <f>B62-B75</f>
+        <v>1.1500000000000004</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="7"/>
+        <v>1.3225000000000009</v>
+      </c>
+      <c r="G62">
+        <f>C62-C75</f>
+        <v>12.800000000000011</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="8"/>
+        <v>163.84000000000029</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="9"/>
+        <v>14.720000000000018</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="10"/>
+        <v>257.228342958685</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="11"/>
+        <v>3.7716570413149952</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="12"/>
+        <v>14.225396837300984</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="13"/>
+        <v>0.79029982429449908</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>10</v>
+      </c>
+      <c r="B63">
+        <v>15</v>
+      </c>
+      <c r="C63">
+        <v>254</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="6"/>
+        <v>225</v>
+      </c>
+      <c r="E63">
+        <f>B63-B75</f>
+        <v>-0.84999999999999964</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="7"/>
+        <v>0.72249999999999936</v>
+      </c>
+      <c r="G63">
+        <f>C63-C75</f>
+        <v>5.8000000000000114</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="8"/>
+        <v>33.640000000000128</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="9"/>
+        <v>-4.9300000000000077</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="10"/>
+        <v>241.52687694358065</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="11"/>
+        <v>12.473123056419354</v>
+      </c>
+      <c r="L63">
+        <f t="shared" si="12"/>
+        <v>155.57879878058009</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="13"/>
+        <v>8.6432665989211159</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>11</v>
+      </c>
+      <c r="B64">
+        <v>13</v>
+      </c>
+      <c r="C64">
+        <v>229</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="E64">
+        <f>B64-B75</f>
+        <v>-2.8499999999999996</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="7"/>
+        <v>8.1224999999999987</v>
+      </c>
+      <c r="G64">
+        <f>C64-C75</f>
+        <v>-19.199999999999989</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="8"/>
+        <v>368.63999999999959</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="9"/>
+        <v>54.719999999999963</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="10"/>
+        <v>225.82541092847623</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="11"/>
+        <v>3.1745890715237692</v>
+      </c>
+      <c r="L64">
+        <f t="shared" si="12"/>
+        <v>10.078015773038148</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="13"/>
+        <v>0.55988976516878597</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>12</v>
+      </c>
+      <c r="B65">
+        <v>16</v>
+      </c>
+      <c r="C65">
+        <v>249</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="6"/>
+        <v>256</v>
+      </c>
+      <c r="E65">
+        <f>B65-B75</f>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="7"/>
+        <v>2.2500000000000107E-2</v>
+      </c>
+      <c r="G65">
+        <f>C65-C75</f>
+        <v>0.80000000000001137</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="8"/>
+        <v>0.64000000000001822</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="9"/>
+        <v>0.12000000000000199</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="10"/>
+        <v>249.37760995113283</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="11"/>
+        <v>-0.37760995113282547</v>
+      </c>
+      <c r="L65">
+        <f t="shared" si="12"/>
+        <v>0.14258927519453485</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="13"/>
+        <v>7.9216263996963812E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>13</v>
+      </c>
+      <c r="B66">
+        <v>17</v>
+      </c>
+      <c r="C66">
+        <v>252</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="6"/>
+        <v>289</v>
+      </c>
+      <c r="E66">
+        <f>B66-B75</f>
+        <v>1.1500000000000004</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="7"/>
+        <v>1.3225000000000009</v>
+      </c>
+      <c r="G66">
+        <f>C66-C75</f>
+        <v>3.8000000000000114</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="8"/>
+        <v>14.440000000000087</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="9"/>
+        <v>4.3700000000000143</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="10"/>
+        <v>257.228342958685</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="11"/>
+        <v>-5.2283429586850048</v>
+      </c>
+      <c r="L66">
+        <f t="shared" si="12"/>
+        <v>27.33557009363107</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="13"/>
+        <v>1.5186427829795039</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>14</v>
+      </c>
+      <c r="B67">
+        <v>19</v>
+      </c>
+      <c r="C67">
+        <v>279</v>
+      </c>
+      <c r="D67">
+        <f t="shared" si="6"/>
+        <v>361</v>
+      </c>
+      <c r="E67">
+        <f>B67-B75</f>
+        <v>3.1500000000000004</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="7"/>
+        <v>9.922500000000003</v>
+      </c>
+      <c r="G67">
+        <f>C67-C75</f>
+        <v>30.800000000000011</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="8"/>
+        <v>948.64000000000067</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="9"/>
+        <v>97.020000000000053</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="10"/>
+        <v>272.92980897378942</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="11"/>
+        <v>6.0701910262105798</v>
+      </c>
+      <c r="L67">
+        <f t="shared" si="12"/>
+        <v>36.847219094687453</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="13"/>
+        <v>2.0470677274826361</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>15</v>
+      </c>
+      <c r="B68">
+        <v>18</v>
+      </c>
+      <c r="C68">
+        <v>262</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="6"/>
+        <v>324</v>
+      </c>
+      <c r="E68">
+        <f>B68-B75</f>
+        <v>2.1500000000000004</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="7"/>
+        <v>4.6225000000000014</v>
+      </c>
+      <c r="G68">
+        <f>C68-C75</f>
+        <v>13.800000000000011</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="8"/>
+        <v>190.44000000000031</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="9"/>
+        <v>29.67000000000003</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="10"/>
+        <v>265.07907596623721</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="11"/>
+        <v>-3.0790759662372125</v>
+      </c>
+      <c r="L68">
+        <f t="shared" si="12"/>
+        <v>9.4807088058596243</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="13"/>
+        <v>0.52670604476997918</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>16</v>
+      </c>
+      <c r="B69">
+        <v>20</v>
+      </c>
+      <c r="C69">
+        <v>275</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="E69">
+        <f>B69-B75</f>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="7"/>
+        <v>17.222500000000004</v>
+      </c>
+      <c r="G69">
+        <f>C69-C75</f>
+        <v>26.800000000000011</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="8"/>
+        <v>718.24000000000058</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="9"/>
+        <v>111.22000000000006</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="10"/>
+        <v>280.78054198134163</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="11"/>
+        <v>-5.7805419813416279</v>
+      </c>
+      <c r="L69">
+        <f t="shared" si="12"/>
+        <v>33.414665598052991</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="13"/>
+        <v>1.8563703110029439</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>17</v>
+      </c>
+      <c r="B70">
+        <v>12</v>
+      </c>
+      <c r="C70">
+        <v>211</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="6"/>
+        <v>144</v>
+      </c>
+      <c r="E70">
+        <f>B70-B75</f>
+        <v>-3.8499999999999996</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="7"/>
+        <v>14.822499999999998</v>
+      </c>
+      <c r="G70">
+        <f>C70-C75</f>
+        <v>-37.199999999999989</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="8"/>
+        <v>1383.8399999999992</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="9"/>
+        <v>143.21999999999994</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="10"/>
+        <v>217.97467792092402</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="11"/>
+        <v>-6.9746779209240231</v>
+      </c>
+      <c r="L70">
+        <f t="shared" si="12"/>
+        <v>48.646132100625053</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="13"/>
+        <v>2.7025628944791698</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>13</v>
+      </c>
+      <c r="C71">
+        <v>229</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="6"/>
+        <v>169</v>
+      </c>
+      <c r="E71">
+        <f>B71-B75</f>
+        <v>-2.8499999999999996</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="7"/>
+        <v>8.1224999999999987</v>
+      </c>
+      <c r="G71">
+        <f>C71-C75</f>
+        <v>-19.199999999999989</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="8"/>
+        <v>368.63999999999959</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="9"/>
+        <v>54.719999999999963</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="10"/>
+        <v>225.82541092847623</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="11"/>
+        <v>3.1745890715237692</v>
+      </c>
+      <c r="L71">
+        <f t="shared" si="12"/>
+        <v>10.078015773038148</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="13"/>
+        <v>0.55988976516878597</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>19</v>
+      </c>
+      <c r="B72">
+        <v>12</v>
+      </c>
+      <c r="C72">
+        <v>218</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="6"/>
+        <v>144</v>
+      </c>
+      <c r="E72">
+        <f>B72-B75</f>
+        <v>-3.8499999999999996</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="7"/>
+        <v>14.822499999999998</v>
+      </c>
+      <c r="G72">
+        <f>C72-C75</f>
+        <v>-30.199999999999989</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="8"/>
+        <v>912.03999999999928</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="9"/>
+        <v>116.26999999999994</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="10"/>
+        <v>217.97467792092402</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="11"/>
+        <v>2.5322079075976944E-2</v>
+      </c>
+      <c r="L72">
+        <f t="shared" si="12"/>
+        <v>6.4120768873002936E-4</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="13"/>
+        <v>3.5622649373890522E-5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>20</v>
+      </c>
+      <c r="B73">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>232</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="6"/>
+        <v>196</v>
+      </c>
+      <c r="E73">
+        <f>B73-B75</f>
+        <v>-1.8499999999999996</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="7"/>
+        <v>3.4224999999999985</v>
+      </c>
+      <c r="G73">
+        <f>C73-C75</f>
+        <v>-16.199999999999989</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="8"/>
+        <v>262.43999999999966</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="9"/>
+        <v>29.969999999999974</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="10"/>
+        <v>233.67614393602844</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="11"/>
+        <v>-1.6761439360284385</v>
+      </c>
+      <c r="L73">
+        <f t="shared" si="12"/>
+        <v>2.8094584942849061</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="13"/>
+        <v>0.15608102746027255</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B74" s="3">
+        <f>SUM(B54:B73)</f>
+        <v>317</v>
+      </c>
+      <c r="C74" s="3">
+        <f>SUM(C54:C73)</f>
+        <v>4964</v>
+      </c>
+      <c r="D74" s="3">
+        <f>SUM(D54:D73)</f>
+        <v>5137</v>
+      </c>
+      <c r="E74" s="3">
+        <f>SUM(E54:E73)</f>
+        <v>7.1054273576010019E-15</v>
+      </c>
+      <c r="F74" s="3">
+        <f t="shared" ref="F74" si="14">SUM(F54:F73)</f>
+        <v>112.55</v>
+      </c>
+      <c r="G74" s="3">
+        <f t="shared" ref="G74" si="15">SUM(G54:G73)</f>
+        <v>2.2737367544323206E-13</v>
+      </c>
+      <c r="H74" s="3">
+        <f t="shared" ref="H74" si="16">SUM(H54:H73)</f>
+        <v>8287.2000000000007</v>
+      </c>
+      <c r="I74" s="3">
+        <f t="shared" ref="I74" si="17">SUM(I54:I73)</f>
+        <v>883.6</v>
+      </c>
+      <c r="J74" s="3">
+        <f t="shared" ref="J74" si="18">SUM(J54:J73)</f>
+        <v>4964.0000000000018</v>
+      </c>
+      <c r="K74" s="3">
+        <f t="shared" ref="K74" si="19">SUM(K54:K73)</f>
+        <v>1.1368683772161603E-13</v>
+      </c>
+      <c r="L74" s="3">
+        <f t="shared" ref="L74" si="20">SUM(L54:L73)</f>
+        <v>1350.2923145268758</v>
+      </c>
+      <c r="M74" s="3">
+        <f t="shared" ref="M74" si="21">SUM(M54:M73)</f>
+        <v>75.016239695937557</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75" s="3">
+        <f>AVERAGE(B54:B73)</f>
+        <v>15.85</v>
+      </c>
+      <c r="C75" s="3">
+        <f>AVERAGE(C54:C73)</f>
+        <v>248.2</v>
+      </c>
+      <c r="D75" s="3">
+        <f>AVERAGE(D54:D73)</f>
+        <v>256.85000000000002</v>
+      </c>
+      <c r="E75" s="3">
+        <f>AVERAGE(E54:E73)</f>
+        <v>3.5527136788005011E-16</v>
+      </c>
+      <c r="F75" s="3">
+        <f t="shared" ref="F75:M75" si="22">AVERAGE(F54:F73)</f>
+        <v>5.6274999999999995</v>
+      </c>
+      <c r="G75" s="3">
+        <f t="shared" si="22"/>
+        <v>1.1368683772161604E-14</v>
+      </c>
+      <c r="H75" s="3">
+        <f t="shared" si="22"/>
+        <v>414.36</v>
+      </c>
+      <c r="I75" s="3">
+        <f t="shared" si="22"/>
+        <v>44.18</v>
+      </c>
+      <c r="J75" s="3">
+        <f t="shared" si="22"/>
+        <v>248.2000000000001</v>
+      </c>
+      <c r="K75" s="3">
+        <f t="shared" si="22"/>
+        <v>5.6843418860808018E-15</v>
+      </c>
+      <c r="L75" s="3">
+        <f t="shared" si="22"/>
+        <v>67.514615726343791</v>
+      </c>
+      <c r="M75" s="3">
+        <f t="shared" si="22"/>
+        <v>3.7508119847968779</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B80" s="8">
+        <f>(M74)/(20*(D75-B75*B75))</f>
+        <v>0.66651479072356468</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="8">
+        <f>B80*(D75)</f>
+        <v>171.1943239973476</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A84" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A85" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="B85" s="5">
+        <f>TINV(1-A85,18)</f>
+        <v>1.7340636066175394</v>
+      </c>
+      <c r="C85" t="s">
+        <v>38</v>
+      </c>
+      <c r="D85" t="s">
+        <v>38</v>
+      </c>
+      <c r="E85">
+        <f>D49-B85*SQRT(B80)</f>
+        <v>6.4350372867876047</v>
+      </c>
+      <c r="F85">
+        <f>D49+B85*SQRT(B80)</f>
+        <v>9.2664287283167948</v>
+      </c>
+      <c r="G85">
+        <f>D50-B85*SQRT(B81)</f>
+        <v>101.0771770433719</v>
+      </c>
+      <c r="H85">
+        <f>D50+B85*SQRT(B81)</f>
+        <v>146.45458661722336</v>
+      </c>
+      <c r="J85" t="s">
+        <v>39</v>
+      </c>
+      <c r="M85" t="s">
+        <v>42</v>
+      </c>
+      <c r="N85">
+        <f>(D49/SQRT(B80))</f>
+        <v>9.6162404067413547</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A86" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="B86" s="5">
+        <f t="shared" ref="B86:B87" si="23">TINV(1-A86,18)</f>
+        <v>2.1009220402410378</v>
+      </c>
+      <c r="C86" t="s">
+        <v>38</v>
+      </c>
+      <c r="D86" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86">
+        <f>D49-B86*SQRT(B80)</f>
+        <v>6.1355327515299551</v>
+      </c>
+      <c r="F86">
+        <f>D49+B86*SQRT(B80)</f>
+        <v>9.5659332635744434</v>
+      </c>
+      <c r="G86">
+        <f>D50-B86*SQRT(B81)</f>
+        <v>96.27715548285174</v>
+      </c>
+      <c r="H86">
+        <f>D50+B86*SQRT(B81)</f>
+        <v>151.25460817774353</v>
+      </c>
+      <c r="J86" t="s">
+        <v>39</v>
+      </c>
+      <c r="M86" t="s">
+        <v>43</v>
+      </c>
+      <c r="N86">
+        <f>(D50/SQRT(B81))</f>
+        <v>9.4592403329483474</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A87" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="B87" s="5">
+        <f t="shared" si="23"/>
+        <v>2.8784404727386073</v>
+      </c>
+      <c r="C87" t="s">
+        <v>38</v>
+      </c>
+      <c r="D87" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87">
+        <f>D49-B87*SQRT(B80)</f>
+        <v>5.5007639267291824</v>
+      </c>
+      <c r="F87">
+        <f>D49+B87*SQRT(B80)</f>
+        <v>10.200702088375216</v>
+      </c>
+      <c r="G87">
+        <f>D50-B87*SQRT(B81)</f>
+        <v>86.104007211929385</v>
+      </c>
+      <c r="H87">
+        <f>D50+B87*SQRT(B81)</f>
+        <v>161.42775644866589</v>
+      </c>
+      <c r="J87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="15" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>51</v>
+      </c>
+      <c r="B90">
+        <f>1-L74/H74</f>
+        <v>0.83706290248493154</v>
+      </c>
+      <c r="C90" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C91" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C92" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A95" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="10"/>
+      <c r="C95" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A96" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="B96" s="5">
+        <f>FINV(1-A96,2,18)</f>
+        <v>2.6239469851339554</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G96" t="s">
+        <v>56</v>
+      </c>
+      <c r="H96">
+        <f>(B90/(1-B90))*18</f>
+        <v>92.472079560244737</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="B97" s="5">
+        <f t="shared" ref="B97:B98" si="24">FINV(1-A97,2,18)</f>
+        <v>3.5545571456617857</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="B98" s="5">
+        <f>FINV(1-A98,2,18)</f>
+        <v>6.0129048348005281</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>58</v>
+      </c>
+      <c r="B101" t="s">
+        <v>59</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" t="s">
+        <v>61</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F101" t="s">
+        <v>63</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H101" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>12</v>
+      </c>
+      <c r="B102">
+        <f>$D$50+$D$49*A102</f>
+        <v>217.97467792092402</v>
+      </c>
+      <c r="C102">
+        <f>B102-$B$85*SQRT($M$74)*SQRT(1/20+((A102-$B$75)^2)/$F$74)</f>
+        <v>211.57266457010775</v>
+      </c>
+      <c r="D102">
+        <f>B102+$B$85*SQRT($M$74)*SQRT(1/20+((A102-$B$75)^2)/$F$74)</f>
+        <v>224.3766912717403</v>
+      </c>
+      <c r="E102">
+        <f>B102-$B$86*SQRT($M$74)*SQRT(1/20+((A102-$B$75)^2)/$F$74)</f>
+        <v>210.21825485817195</v>
+      </c>
+      <c r="F102">
+        <f>B102+$B$86*SQRT($M$74)*SQRT(1/20+((A102-$B$75)^2)/$F$74)</f>
+        <v>225.7311009836761</v>
+      </c>
+      <c r="G102">
+        <f>B102-$B$87*SQRT($M$74)*SQRT(1/20+((A102-$B$75)^2)/$F$74)</f>
+        <v>207.34772383130573</v>
+      </c>
+      <c r="H102">
+        <f>B102+$B$87*SQRT($M$74)*SQRT(1/20+((A102-$B$75)^2)/$F$74)</f>
+        <v>228.60163201054232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>13</v>
+      </c>
+      <c r="B103">
+        <f t="shared" ref="B103:B110" si="25">$D$50+$D$49*A103</f>
+        <v>225.82541092847623</v>
+      </c>
+      <c r="C103">
+        <f t="shared" ref="C103:C110" si="26">B103-$B$85*SQRT($M$74)*SQRT(1/20+((A103-$B$75)^2)/$F$74)</f>
+        <v>220.57587069721512</v>
+      </c>
+      <c r="D103">
+        <f t="shared" ref="D103:D110" si="27">B103+$B$85*SQRT($M$74)*SQRT(1/20+((A103-$B$75)^2)/$F$74)</f>
+        <v>231.07495115973734</v>
+      </c>
+      <c r="E103">
+        <f t="shared" ref="E103:E110" si="28">B103-$B$86*SQRT($M$74)*SQRT(1/20+((A103-$B$75)^2)/$F$74)</f>
+        <v>219.46527815658709</v>
+      </c>
+      <c r="F103">
+        <f t="shared" ref="F103:F110" si="29">B103+$B$86*SQRT($M$74)*SQRT(1/20+((A103-$B$75)^2)/$F$74)</f>
+        <v>232.18554370036537</v>
+      </c>
+      <c r="G103">
+        <f t="shared" ref="G103:G110" si="30">B103-$B$87*SQRT($M$74)*SQRT(1/20+((A103-$B$75)^2)/$F$74)</f>
+        <v>217.1114923575156</v>
+      </c>
+      <c r="H103">
+        <f t="shared" ref="H103:H110" si="31">B103+$B$87*SQRT($M$74)*SQRT(1/20+((A103-$B$75)^2)/$F$74)</f>
+        <v>234.53932949943686</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>14</v>
+      </c>
+      <c r="B104">
+        <f t="shared" si="25"/>
+        <v>233.67614393602844</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="26"/>
+        <v>229.41727564940459</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="27"/>
+        <v>237.93501222265229</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="28"/>
+        <v>228.51626962939633</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="29"/>
+        <v>238.83601824266054</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="30"/>
+        <v>226.60668074131138</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="31"/>
+        <v>240.7456071307455</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>15</v>
+      </c>
+      <c r="B105">
+        <f t="shared" si="25"/>
+        <v>241.52687694358065</v>
+      </c>
+      <c r="C105">
+        <f t="shared" si="26"/>
+        <v>237.95943608582644</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="27"/>
+        <v>245.09431780133485</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="28"/>
+        <v>237.2047084275527</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="29"/>
+        <v>245.84904545960859</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="30"/>
+        <v>235.60514136832623</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="31"/>
+        <v>247.44861251883506</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>16</v>
+      </c>
+      <c r="B106">
+        <f t="shared" si="25"/>
+        <v>249.37760995113283</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="26"/>
+        <v>246.01253963806056</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="27"/>
+        <v>252.74268026420509</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="28"/>
+        <v>245.30062548486831</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="29"/>
+        <v>253.45459441739735</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="30"/>
+        <v>243.79179721289529</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="31"/>
+        <v>254.96342268937036</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>17</v>
+      </c>
+      <c r="B107">
+        <f t="shared" si="25"/>
+        <v>257.228342958685</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="26"/>
+        <v>253.49616518989521</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="27"/>
+        <v>260.96052072747483</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="28"/>
+        <v>252.70658579670709</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="29"/>
+        <v>261.75010012066292</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="30"/>
+        <v>251.03315409701756</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="31"/>
+        <v>263.42353182035242</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>18</v>
+      </c>
+      <c r="B108">
+        <f t="shared" si="25"/>
+        <v>265.07907596623721</v>
+      </c>
+      <c r="C108">
+        <f t="shared" si="26"/>
+        <v>260.54663817500835</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="27"/>
+        <v>269.61151375746607</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="28"/>
+        <v>259.58775580054368</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="29"/>
+        <v>270.57039613193075</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="30"/>
+        <v>257.55550397691934</v>
+      </c>
+      <c r="H108">
+        <f t="shared" si="31"/>
+        <v>272.60264795555508</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>19</v>
+      </c>
+      <c r="B109">
+        <f t="shared" si="25"/>
+        <v>272.92980897378942</v>
+      </c>
+      <c r="C109">
+        <f t="shared" si="26"/>
+        <v>267.34722690878999</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="27"/>
+        <v>278.51239103878885</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="28"/>
+        <v>266.16617604991455</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="29"/>
+        <v>279.69344189766429</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="30"/>
+        <v>263.66306114691855</v>
+      </c>
+      <c r="H109">
+        <f t="shared" si="31"/>
+        <v>282.19655680066029</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>20</v>
+      </c>
+      <c r="B110">
+        <f t="shared" si="25"/>
+        <v>280.78054198134163</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="26"/>
+        <v>274.0132795037124</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="27"/>
+        <v>287.54780445897086</v>
+      </c>
+      <c r="E110">
+        <f t="shared" si="28"/>
+        <v>272.58159769977624</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="29"/>
+        <v>288.97948626290702</v>
+      </c>
+      <c r="G110">
+        <f t="shared" si="30"/>
+        <v>269.54729648162817</v>
+      </c>
+      <c r="H110">
+        <f t="shared" si="31"/>
+        <v>292.01378748105509</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A167" s="12"/>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="15" x14ac:dyDescent="0.35">
+      <c r="A172" s="11"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Processing of experimental data/Lab 3/Lab3.xlsx
+++ b/Processing of experimental data/Lab 3/Lab3.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Prog\BSUIR-Labs\Processing of experimental data\Lab 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3630A469-0951-494E-8409-5D070595A6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D512294-4F3A-4BF1-9A09-2741C0A3CF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{68418C94-6E50-41DE-9C16-B716F6666BB9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{68418C94-6E50-41DE-9C16-B716F6666BB9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Part1" sheetId="1" r:id="rId1"/>
+    <sheet name="Part2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
   <si>
     <t>t</t>
   </si>
@@ -277,12 +278,111 @@
   <si>
     <t>Это позволяет считать предпосылки метода наименьших квадратов выполненными, а модель – адекватной.</t>
   </si>
+  <si>
+    <t>ВЫВОД ИТОГОВ</t>
+  </si>
+  <si>
+    <t>Регрессионная статистика</t>
+  </si>
+  <si>
+    <t>Множественный R</t>
+  </si>
+  <si>
+    <t>R-квадрат</t>
+  </si>
+  <si>
+    <t>Нормированный R-квадрат</t>
+  </si>
+  <si>
+    <t>Стандартная ошибка</t>
+  </si>
+  <si>
+    <t>Наблюдения</t>
+  </si>
+  <si>
+    <t>Дисперсионный анализ</t>
+  </si>
+  <si>
+    <t>Регрессия</t>
+  </si>
+  <si>
+    <t>Остаток</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
+  <si>
+    <t>Y-пересечение</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Значимость F</t>
+  </si>
+  <si>
+    <t>Коэффициенты</t>
+  </si>
+  <si>
+    <t>t-статистика</t>
+  </si>
+  <si>
+    <t>P-Значение</t>
+  </si>
+  <si>
+    <t>Нижние 95%</t>
+  </si>
+  <si>
+    <t>Верхние 95%</t>
+  </si>
+  <si>
+    <t>Нижние 95,0%</t>
+  </si>
+  <si>
+    <t>Верхние 95,0%</t>
+  </si>
+  <si>
+    <t>Переменная X 1</t>
+  </si>
+  <si>
+    <t>ВЫВОД ОСТАТКА</t>
+  </si>
+  <si>
+    <t>Наблюдение</t>
+  </si>
+  <si>
+    <t>Предсказанное Y</t>
+  </si>
+  <si>
+    <t>Остатки</t>
+  </si>
+  <si>
+    <t>На графике остатки расположены случайным образом вокруг нулевой линии, отсутствует систематический тренд (например, сначала все отрицательные, потом положительные)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> и не видно изменения разброса (гомоскедастичность). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Это говорит о том, что предпосылки метода наименьших квадратов выполняются: остатки независимы, имеют постоянную дисперсию и в среднем равны нулю. </t>
+  </si>
+  <si>
+    <t>Следовательно, построенная модель линейной регрессии адекватна и может использоваться для прогнозирования</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +434,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -361,7 +470,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -369,11 +478,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -402,6 +531,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,7 +662,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$B$2:$B$22</c:f>
+              <c:f>Part1!$B$2:$B$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
@@ -594,7 +731,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$C$2:$C$21</c:f>
+              <c:f>Part1!$C$2:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -869,7 +1006,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -892,7 +1029,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:f>Part1!$A$102:$A$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -928,7 +1065,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$B$102:$B$110</c:f>
+              <c:f>Part1!$B$102:$B$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1001,7 +1138,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:f>Part1!$A$102:$A$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1037,7 +1174,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$C$102:$C$110</c:f>
+              <c:f>Part1!$C$102:$C$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1110,7 +1247,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:f>Part1!$A$102:$A$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1146,7 +1283,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$E$102:$E$110</c:f>
+              <c:f>Part1!$E$102:$E$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1219,7 +1356,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:f>Part1!$A$102:$A$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1255,7 +1392,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$G$102:$G$110</c:f>
+              <c:f>Part1!$G$102:$G$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1328,7 +1465,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:f>Part1!$A$102:$A$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1364,7 +1501,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$D$102:$D$110</c:f>
+              <c:f>Part1!$D$102:$D$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1437,7 +1574,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:f>Part1!$A$102:$A$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1473,7 +1610,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$F$102:$F$110</c:f>
+              <c:f>Part1!$F$102:$F$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1550,7 +1687,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$102:$A$110</c:f>
+              <c:f>Part1!$A$102:$A$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1586,7 +1723,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$H$102:$H$110</c:f>
+              <c:f>Part1!$H$102:$H$110</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -1869,7 +2006,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Лист1!$A$54:$A$73</c:f>
+              <c:f>Part1!$A$54:$A$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1938,7 +2075,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Лист1!$K$54:$K$73</c:f>
+              <c:f>Part1!$K$54:$K$73</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2027,6 +2164,7 @@
         <c:axId val="71143840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="20"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2144,6 +2282,719 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="71143840"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-BY"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Переменная </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>X 1 </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>График остатков</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Part2!$A$1:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Part2!$M$25:$M$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>-11.676143936028438</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8.3776099511328255</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-14.228342958685005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.07019102621058</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-12.079075966237212</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4731230564193538</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.323856063971562</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.920924033762788</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.7716570413149952</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.473123056419354</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.1745890715237692</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.37760995113282547</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.2283429586850048</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.0701910262105798</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-3.0790759662372125</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-5.7805419813416279</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-6.9746779209240231</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.1745890715237692</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.5322079075976944E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-1.6761439360284385</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0533-4850-85B3-316E7899CFCB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1745732720"/>
+        <c:axId val="1745730800"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1745732720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Переменная </a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>X 1</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1745730800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1745730800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU"/>
+                  <a:t>Остатки</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1745732720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-BY"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>yt</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Part2!$A$1:$A$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Part2!$B$1:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>222</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>241</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>243</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>253</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>247</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>261</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>254</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>249</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>252</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>279</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>262</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>229</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>218</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>232</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BA5F-4139-8108-A424CAB05B02}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1745733680"/>
+        <c:axId val="1745726000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1745733680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="21"/>
+          <c:min val="12"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1745726000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1745726000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="211"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-BY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1745733680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2319,6 +3170,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -3339,6 +4230,522 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -3959,6 +5366,83 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C72FFAC7-1DE3-6F0E-95D0-C902E927D7B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>121920</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08A721E9-852C-87FD-868C-EB73949B63E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6843,7 +8327,7 @@
         <v>0.95</v>
       </c>
       <c r="B97" s="5">
-        <f t="shared" ref="B97:B98" si="24">FINV(1-A97,2,18)</f>
+        <f t="shared" ref="B97" si="24">FINV(1-A97,2,18)</f>
         <v>3.5545571456617857</v>
       </c>
       <c r="C97" s="5" t="s">
@@ -7230,4 +8714,614 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CDA74FD-7E7B-4182-AA7B-C767C55BDC29}">
+  <dimension ref="A1:S73"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="20" width="40.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>14</v>
+      </c>
+      <c r="B1">
+        <v>222</v>
+      </c>
+      <c r="K1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>243</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="16"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>285</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="L4" s="13">
+        <v>0.91491141783504448</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>253</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="L5" s="13">
+        <v>0.83706290248493131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>247</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="13">
+        <v>0.82801084151187199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>246</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" s="13">
+        <v>8.6611915863775693</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>276</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>254</v>
+      </c>
+      <c r="K10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>229</v>
+      </c>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>249</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="L12" s="13">
+        <v>1</v>
+      </c>
+      <c r="M12" s="13">
+        <v>6936.9076854731238</v>
+      </c>
+      <c r="N12" s="13">
+        <v>6936.9076854731238</v>
+      </c>
+      <c r="O12" s="13">
+        <v>92.472079560244637</v>
+      </c>
+      <c r="P12" s="13">
+        <v>1.6253134755728169E-8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>252</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="13">
+        <v>18</v>
+      </c>
+      <c r="M13" s="13">
+        <v>1350.2923145268769</v>
+      </c>
+      <c r="N13" s="13">
+        <v>75.0162396959376</v>
+      </c>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+    </row>
+    <row r="14" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>279</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" s="14">
+        <v>19</v>
+      </c>
+      <c r="M14" s="14">
+        <v>8287.2000000000007</v>
+      </c>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+    </row>
+    <row r="15" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>275</v>
+      </c>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="N16" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="S16" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>211</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" s="13">
+        <v>123.76588183029763</v>
+      </c>
+      <c r="M17" s="13">
+        <v>13.084124884658832</v>
+      </c>
+      <c r="N17" s="13">
+        <v>9.4592403329483208</v>
+      </c>
+      <c r="O17" s="13">
+        <v>2.0864463881585575E-8</v>
+      </c>
+      <c r="P17" s="13">
+        <v>96.277155482851668</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>151.25460817774359</v>
+      </c>
+      <c r="R17" s="13">
+        <v>96.277155482851668</v>
+      </c>
+      <c r="S17" s="13">
+        <v>151.25460817774359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18">
+        <v>229</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="L18" s="14">
+        <v>7.8507330075521997</v>
+      </c>
+      <c r="M18" s="14">
+        <v>0.81640357098898597</v>
+      </c>
+      <c r="N18" s="14">
+        <v>9.6162404067413281</v>
+      </c>
+      <c r="O18" s="14">
+        <v>1.6253134755728169E-8</v>
+      </c>
+      <c r="P18" s="14">
+        <v>6.1355327515299507</v>
+      </c>
+      <c r="Q18" s="14">
+        <v>9.5659332635744487</v>
+      </c>
+      <c r="R18" s="14">
+        <v>6.1355327515299507</v>
+      </c>
+      <c r="S18" s="14">
+        <v>9.5659332635744487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>12</v>
+      </c>
+      <c r="B19">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>14</v>
+      </c>
+      <c r="B20">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K22" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K24" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K25" s="13">
+        <v>1</v>
+      </c>
+      <c r="L25" s="13">
+        <v>233.67614393602844</v>
+      </c>
+      <c r="M25" s="13">
+        <v>-11.676143936028438</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K26" s="13">
+        <v>2</v>
+      </c>
+      <c r="L26" s="13">
+        <v>249.37760995113283</v>
+      </c>
+      <c r="M26" s="13">
+        <v>-8.3776099511328255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K27" s="13">
+        <v>3</v>
+      </c>
+      <c r="L27" s="13">
+        <v>257.228342958685</v>
+      </c>
+      <c r="M27" s="13">
+        <v>-14.228342958685005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K28" s="13">
+        <v>4</v>
+      </c>
+      <c r="L28" s="13">
+        <v>272.92980897378942</v>
+      </c>
+      <c r="M28" s="13">
+        <v>12.07019102621058</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K29" s="13">
+        <v>5</v>
+      </c>
+      <c r="L29" s="13">
+        <v>265.07907596623721</v>
+      </c>
+      <c r="M29" s="13">
+        <v>-12.079075966237212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K30" s="13">
+        <v>6</v>
+      </c>
+      <c r="L30" s="13">
+        <v>241.52687694358065</v>
+      </c>
+      <c r="M30" s="13">
+        <v>5.4731230564193538</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K31" s="13">
+        <v>7</v>
+      </c>
+      <c r="L31" s="13">
+        <v>233.67614393602844</v>
+      </c>
+      <c r="M31" s="13">
+        <v>12.323856063971562</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="K32" s="13">
+        <v>8</v>
+      </c>
+      <c r="L32" s="13">
+        <v>265.07907596623721</v>
+      </c>
+      <c r="M32" s="13">
+        <v>10.920924033762788</v>
+      </c>
+    </row>
+    <row r="33" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K33" s="13">
+        <v>9</v>
+      </c>
+      <c r="L33" s="13">
+        <v>257.228342958685</v>
+      </c>
+      <c r="M33" s="13">
+        <v>3.7716570413149952</v>
+      </c>
+    </row>
+    <row r="34" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K34" s="13">
+        <v>10</v>
+      </c>
+      <c r="L34" s="13">
+        <v>241.52687694358065</v>
+      </c>
+      <c r="M34" s="13">
+        <v>12.473123056419354</v>
+      </c>
+    </row>
+    <row r="35" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K35" s="13">
+        <v>11</v>
+      </c>
+      <c r="L35" s="13">
+        <v>225.82541092847623</v>
+      </c>
+      <c r="M35" s="13">
+        <v>3.1745890715237692</v>
+      </c>
+    </row>
+    <row r="36" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K36" s="13">
+        <v>12</v>
+      </c>
+      <c r="L36" s="13">
+        <v>249.37760995113283</v>
+      </c>
+      <c r="M36" s="13">
+        <v>-0.37760995113282547</v>
+      </c>
+    </row>
+    <row r="37" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K37" s="13">
+        <v>13</v>
+      </c>
+      <c r="L37" s="13">
+        <v>257.228342958685</v>
+      </c>
+      <c r="M37" s="13">
+        <v>-5.2283429586850048</v>
+      </c>
+    </row>
+    <row r="38" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K38" s="13">
+        <v>14</v>
+      </c>
+      <c r="L38" s="13">
+        <v>272.92980897378942</v>
+      </c>
+      <c r="M38" s="13">
+        <v>6.0701910262105798</v>
+      </c>
+    </row>
+    <row r="39" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K39" s="13">
+        <v>15</v>
+      </c>
+      <c r="L39" s="13">
+        <v>265.07907596623721</v>
+      </c>
+      <c r="M39" s="13">
+        <v>-3.0790759662372125</v>
+      </c>
+    </row>
+    <row r="40" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K40" s="13">
+        <v>16</v>
+      </c>
+      <c r="L40" s="13">
+        <v>280.78054198134163</v>
+      </c>
+      <c r="M40" s="13">
+        <v>-5.7805419813416279</v>
+      </c>
+    </row>
+    <row r="41" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K41" s="13">
+        <v>17</v>
+      </c>
+      <c r="L41" s="13">
+        <v>217.97467792092402</v>
+      </c>
+      <c r="M41" s="13">
+        <v>-6.9746779209240231</v>
+      </c>
+    </row>
+    <row r="42" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K42" s="13">
+        <v>18</v>
+      </c>
+      <c r="L42" s="13">
+        <v>225.82541092847623</v>
+      </c>
+      <c r="M42" s="13">
+        <v>3.1745890715237692</v>
+      </c>
+    </row>
+    <row r="43" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K43" s="13">
+        <v>19</v>
+      </c>
+      <c r="L43" s="13">
+        <v>217.97467792092402</v>
+      </c>
+      <c r="M43" s="13">
+        <v>2.5322079075976944E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="11:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K44" s="14">
+        <v>20</v>
+      </c>
+      <c r="L44" s="14">
+        <v>233.67614393602844</v>
+      </c>
+      <c r="M44" s="14">
+        <v>-1.6761439360284385</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C70" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C72" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>